--- a/report/单人执行计划.xlsx
+++ b/report/单人执行计划.xlsx
@@ -10,6 +10,7 @@
     <sheet name="单人计划总览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="周计划明细" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="对比与AI假设" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="风险与弊端分析" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -192,8 +193,55 @@
       <color rgb="00059669"/>
       <sz val="8.800000000000001"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -245,6 +293,16 @@
         <fgColor rgb="00FFF7ED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B91C1C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -272,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -366,6 +424,29 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2517,10 +2598,729 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A24:D24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>单人（或 1+1）Vibe Coding 模式 · 弊端与风险分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>结论先行：快是真的快，但"快"的代价被转移到了维护期和合规风险上——本表逐条列出弊端、后果与（可选）缓解措施，供决策时对照权衡</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>风险等级</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>弊端</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>具体表现</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>后果</t>
+        </is>
+      </c>
+      <c r="E4" s="36" t="inlineStr">
+        <is>
+          <t>缓解措施（可选）</t>
+        </is>
+      </c>
+      <c r="F4" s="36" t="inlineStr">
+        <is>
+          <t>残余风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B5" s="38" t="inlineStr">
+        <is>
+          <t>无代码评审（No Review）</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>AI 生成的代码由同一人验收，写作者的盲区 = 验收者的盲区；AI 幻觉代码（看似正确实则边界错误）无人拦截</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>逻辑缺陷流入生产；边界条件（空值/并发/超长字符）成灾；后期修一个 bug 引三个</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>每两周请一位外部工程师做 2h 关键模块评审（UC 权限/掩码/处置/加密）；AI 双模型交叉审查（A 生成 B 审）</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>评审覆盖有限，非关键模块仍是盲区</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>测试覆盖不足</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>为赶速度只测"能跑通的主路径"；异常路径/并发/大数据量场景无用例；AI 生成的测试往往只验证自己生成逻辑（自我印证）</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>上线后 P1/P2 缺陷集中爆发；回归无安全网，不敢改代码；数据对账出错可能污染湖仓</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>对账/权限/处置三个模块强制人工设计用例（不用 AI 生成）；CI 覆盖率门禁 &gt;70% 硬卡；UAT 预演一次</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>数据类 bug（错不报错、静默丢数）仍难发现</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>架构决策无制衡</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>一人拍板所有技术选型（存储结构/权限模型/任务编排），无人挑战；AI 倾向给出"通用方案"而非"本项目最优"</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>错误的结构性决策（如分区键选错）到数据量大时才暴露，返工成本 = 重新入湖</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>W1/W5 两个节点做一次 30 分钟外部架构 sanity check；重大决策写 ADR 并请平台团队看一眼</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>隐性耦合与坏味道依然会积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>代码可维护性差（"能跑就行"）</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>AI 生成代码风格漂移、重复代码多、命名不一致；单人赶进度优先 Copy-Paste 而非抽象；无重构节奏</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>六个月后自己都看不懂；加新系统接入时改动风险大；技术债复利累积</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>每周固定半天"还债时间"只做重构；用 AI 反向生成模块 README 与调用图；关键模块保持 &lt;300 行</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>债只会减缓不会消失</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>安全隐患放大</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>单人自查 = 自己查自己；四道 CI 门禁（SAST/依赖/密钥/镜像）是机器规则，挡不住逻辑漏洞（如越权判断写错位置）</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>权限绕过/数据越界访问流入生产——这是归档系统最不能容忍的缺陷类型（合规直接挂）</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>权限矩阵（谁可访问什么）由业务方书面确认；上线前做一次渗透测试（哪怕半天）；掩码旁路专项用例</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>未渗透到的攻击面仍是盲区</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="36" t="inlineStr">
+        <is>
+          <t>风险等级</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>弊端</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>具体表现</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>后果</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>缓解措施（可选）</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>残余风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B12" s="38" t="inlineStr">
+        <is>
+          <t>无专职文档人，文档质量低</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>开发完了才补文档（V 版计划 W15~17），靠记忆与 git 反推；AI 反生成的文档"看起来完整"但缺设计意图与取舍理由</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>文档与代码两张皮；交接/审计时文档不能作为可靠依据；合规审批材料说服力弱</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>开发期强制"一句话 ADR + 提交说明"习惯（成本极低）；文档补齐后请业务方/审批方实际走查一遍</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>设计意图（为什么这么做）永久丢失</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>巴士因子 = 1（Bus Factor）</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>全部知识在一个人脑子里（源库怪癖/权限配置/处置规则/踩坑记录）；AI 对话上下文不构成可交接资产</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>此人请假/离职/生病，项目即停摆；接手者面对无文档系统 + 无评审代码，接手成本极高</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>关键配置全部脚本化进 git（不留本地）；每周五 30 分钟自我"交接演练"：假设下周换人，缺什么就补什么</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>隐性知识仍随人走</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>需求理解偏差无人纠偏</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>单人理解需求 → 单人实现 → 单人验收，闭环里没有第二双眼睛；AI 不会质疑需求本身</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>做出来的"对的错误"——精准实现了理解错的需求；UAT 才发现 = 返工整条链路</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>每个 Sprint 让业务方看一次演示（哪怕 15 分钟）；用户故事验收标准三方（说/写/做）核对</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>小颗粒理解偏差仍会漏网</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>风险等级</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>弊端</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>具体表现</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="inlineStr">
+        <is>
+          <t>后果</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>缓解措施（可选）</t>
+        </is>
+      </c>
+      <c r="F16" s="36" t="inlineStr">
+        <is>
+          <t>残余风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>单人串行 = 单点故障</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>任何等待（资源 3~5 天/CC 账号 1~2 周/审批）都让全线停摆；团队版可并行换任务，单人版只能干等或跳步</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>20 周计划的缓冲只有 3 周；一次两周的延期就把缓冲吃光</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>外部依赖 D1 全部发起；等待期预排"无依赖任务池"（文档模板/测试数据/脚本打磨）</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>关键路径上任一硬阻塞仍直接顺延</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>AI 提效假设可能落空</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>×2.2 是加权假设：CRUD/前端能 ×3，但数据管道（调试/对账）只有 ×1.5；遇到 AI 不熟的领域（Iceberg/Databricks 新特性）可能 ×1</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>W5 校准点若发现实际 ×1.5，总工期拉到 26~28 周；领导预期与实际脱节</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>W5 MVP 是硬校准点：实测已完成人天 vs 计划，偏差 &gt;20% 立即上报调整（加人或延期）</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>沉没成本压力下容易硬扛不报</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B19" s="38" t="inlineStr">
+        <is>
+          <t>"AI 快"诱发范围失控</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>AI 生成太容易，倾向"顺手多做"（多生成页面/多加配置项）；无 PO 管范围，Scope 悄悄膨胀</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>每个功能都 80% 完成但没有一个 100%；核心链路（迁移/处置/权限）被摊薄</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>严格按 8 域功能清单执行，超出的一律进 backlog；每周自查"本周产出是否在清单内"</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>隐性需求（业务方口头加的）仍会混入</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>质量债在 UAT 集中爆发</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>团队版 Bug 在每个 Sprint Review 被业务方暴露；单人版到 W14 才有正式 UAT，问题积压</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>UAT 周发现成批问题，修复时间不够 → 上线顺延 → 连锁吃掉文档期</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>每两周一次 15 分钟业务方演示（兼做迷你 UAT）；W13 预演做全量 8 域走查</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>非演示路径的缺陷仍积压</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>风险等级</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>弊端</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="inlineStr">
+        <is>
+          <t>具体表现</t>
+        </is>
+      </c>
+      <c r="D22" s="36" t="inlineStr">
+        <is>
+          <t>后果</t>
+        </is>
+      </c>
+      <c r="E22" s="36" t="inlineStr">
+        <is>
+          <t>缓解措施（可选）</t>
+        </is>
+      </c>
+      <c r="F22" s="36" t="inlineStr">
+        <is>
+          <t>残余风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B23" s="38" t="inlineStr">
+        <is>
+          <t>合规举证能力弱</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>归档系统要应对等保/个保法/审计：单人模式无独立 QA 签字、无评审记录、文档后补——举证链完整度天然低于团队版</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>监管抽查时"谁验证的/何时验证/依据什么"答不上；审批被退回补材料</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>CI 流水线记录 + 测试报告 + ADR 作为机器举证链；关键合规项（销毁/掩码）录像留证</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>人为判断环节仍缺第二签字</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B24" s="38" t="inlineStr">
+        <is>
+          <t>无职责分离（SoD 冲突）</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>同一人写代码 + 配权限 + 执行迁移 + 验证对账——开发/运维/验证三权合一，审计视角这是红线</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>内部审计可能直接提不符合项；销毁操作无第二人复核（不可逆动作单点判断）</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>销毁/权限变更两类操作强制引入第二人审批（业务方或平台团队点确认即可）；生产发布走 DevOps Environments 审批留痕</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>日常小变更仍难做到双人</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B25" s="38" t="inlineStr">
+        <is>
+          <t>人员成长与组织能力为零</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>团队版沉淀下 4~5 人可复用的湖仓能力（后续接第 2~N 系统的班底）；单人版结束 = 能力随人离开</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>后续 12 个系统接入要么原班人马（若还在），要么从头再来；组织没有获得资产</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>若后续确有 12 系统接入计划，建议至少 R2 阶段带 1 名内部工程师"做中学"</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>培养节奏赶不上接入排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B26" s="38" t="inlineStr">
+        <is>
+          <t>职业倦怠与判断力衰减</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>连续 20 周一人扛全栈 + 值守 + 文档；关键判断（如 Go/No-Go）疲劳状态下做出</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>后期决策质量下降；上线周 48h 值守后立即补文档，错误率上升</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>W14 上线后强制休整 2~3 天再进文档期；Go/No-Go 决策请业务方共同背书</t>
+        </is>
+      </c>
+      <c r="F26" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>总结：什么时候可以接受单人/1+1 模式，什么时候不该</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>✔ 相对适合：内部工具属性强、合规压力可协商、后续系统接入量少、领导明确接受"快但糙"的权衡、且本人对全栈有把握</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>✘ 不适合：强合规监管（等保三级/个保法硬约束）、后续还有 11+ 系统要接入（能力资产重要）、数据不可逆操作多（销毁/迁移）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>⚖ 折中建议（1+1 模式）：原计划 + 1 名兼职评审/测试人（每周 1~2 天），花 ~15% 成本覆盖掉"无评审/无测试"两个最高危弊端</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>⚖ 最小代价三件事：① 两个关键节点外部评审（W1/W5）② 销毁与权限变更双审批 ③ 开发期 ADR 一句话习惯——成本 &lt;5% 额外，挡掉大半结构性风险</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>